--- a/outputs/monitor_xlsx/20260318.xlsx
+++ b/outputs/monitor_xlsx/20260318.xlsx
@@ -544,10 +544,6 @@
           <t>+1.38%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-3.19%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>-0.17%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-0.53%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+12.16%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>+2.76%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,7 +671,6 @@
           <t>90.21億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-233.16億</t>
@@ -733,7 +708,6 @@
           <t>-2.88億</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>33.05億</t>
@@ -744,8 +718,6 @@
           <t>165.23億</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,15 +735,11 @@
           <t>155.06%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>149.34%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -789,11 +757,6 @@
           <t>186.96億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,15 +774,11 @@
           <t>14569口</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>12700口</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,7 +796,6 @@
           <t>-68.05億</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>-34.93億</t>
@@ -942,10 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1067,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1102,6 +1056,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2380,6 +2335,112 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7220</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="E23" t="n">
+        <v>433</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" t="n">
+        <v>37</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I23" t="n">
+        <v>65</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" t="n">
+        <v>250</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1254</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-8982</v>
+      </c>
+      <c r="N23" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1565</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5154</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>141</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-899</v>
+      </c>
+      <c r="H24" t="n">
+        <v>366</v>
+      </c>
+      <c r="I24" t="n">
+        <v>642</v>
+      </c>
+      <c r="J24" t="n">
+        <v>61</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3448</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16154</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-106285</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260318.xlsx
+++ b/outputs/monitor_xlsx/20260318.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>34348.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+1.38%</t>
-        </is>
-      </c>
+          <t>+1.51%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4841.5$</t>
+          <t>329.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3.19%</t>
-        </is>
-      </c>
+          <t>+2.61%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>34263.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
+          <t>+1.37%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7795.13</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.53%</t>
-        </is>
-      </c>
+          <t>+1.38%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>4889.9$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+12.16%</t>
-        </is>
-      </c>
+          <t>-2.22%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>98.87$</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+2.76%</t>
-        </is>
-      </c>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>90.21億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-233.16億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-1165.78億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-199.89億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3997.76億</t>
-        </is>
-      </c>
+          <t>7795.13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.88億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>33.05億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>165.23億</t>
-        </is>
-      </c>
+          <t>25.09</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+12.16%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>155.06%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>149.34%</t>
-        </is>
-      </c>
+          <t>96.32$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +765,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>186.96億</t>
+          <t>90.21億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-136.56億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-682.79億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -766,54 +803,137 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14569口</t>
-        </is>
-      </c>
+          <t>-2.88億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12700口</t>
-        </is>
-      </c>
+          <t>7.09億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>35.45億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>149.34%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>186.96億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14569口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>14461口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-68.05億</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-34.93億</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-174.66億</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-7.6億</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-151.91億</t>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-51.45億</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-257.23億</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-19.16億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-383.21億</t>
         </is>
       </c>
     </row>
@@ -860,7 +980,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-233.16億</t>
+          <t>-136.56億</t>
         </is>
       </c>
     </row>
@@ -872,7 +992,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1165.78億</t>
+          <t>-682.79億</t>
         </is>
       </c>
     </row>
@@ -884,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-199.89億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -896,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-3997.76億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33.05億</t>
+          <t>7.09億</t>
         </is>
       </c>
     </row>
@@ -920,7 +1044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>165.23億</t>
+          <t>35.45億</t>
         </is>
       </c>
     </row>
@@ -939,7 +1063,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-34.93億</t>
+          <t>-51.45億</t>
         </is>
       </c>
     </row>
@@ -951,7 +1075,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-174.66億</t>
+          <t>-257.23億</t>
         </is>
       </c>
     </row>
@@ -963,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-7.6億</t>
+          <t>-19.16億</t>
         </is>
       </c>
     </row>
@@ -975,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-151.91億</t>
+          <t>-383.21億</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12700口</t>
+          <t>14461口</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1203,13 +1320,13 @@
         <v>-5532</v>
       </c>
       <c r="H4" t="n">
-        <v>-206158</v>
+        <v>-92176</v>
       </c>
       <c r="I4" t="n">
         <v>2000</v>
       </c>
       <c r="J4" t="n">
-        <v>12082</v>
+        <v>5150</v>
       </c>
       <c r="K4" t="n">
         <v>13655</v>
@@ -1218,20 +1335,12 @@
         <v>12630</v>
       </c>
       <c r="M4" t="n">
-        <v>65985</v>
+        <v>54076</v>
       </c>
       <c r="N4" t="n">
         <v>-4479813</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1266,13 +1375,13 @@
         <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>-596</v>
+        <v>-229</v>
       </c>
       <c r="I5" t="n">
         <v>-2</v>
       </c>
       <c r="J5" t="n">
-        <v>-308</v>
+        <v>-156</v>
       </c>
       <c r="K5" t="n">
         <v>36</v>
@@ -1281,20 +1390,12 @@
         <v>2923</v>
       </c>
       <c r="M5" t="n">
-        <v>13957</v>
+        <v>11281</v>
       </c>
       <c r="N5" t="n">
         <v>-78826</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1329,13 +1430,13 @@
         <v>1386</v>
       </c>
       <c r="H6" t="n">
-        <v>3767</v>
+        <v>3734</v>
       </c>
       <c r="I6" t="n">
         <v>53</v>
       </c>
       <c r="J6" t="n">
-        <v>935</v>
+        <v>-180</v>
       </c>
       <c r="K6" t="n">
         <v>366</v>
@@ -1344,20 +1445,12 @@
         <v>5501</v>
       </c>
       <c r="M6" t="n">
-        <v>29181</v>
+        <v>23315</v>
       </c>
       <c r="N6" t="n">
         <v>-649114</v>
       </c>
-      <c r="O6" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1392,13 +1485,13 @@
         <v>373</v>
       </c>
       <c r="H7" t="n">
-        <v>-27961</v>
+        <v>-32020</v>
       </c>
       <c r="I7" t="n">
         <v>-144</v>
       </c>
       <c r="J7" t="n">
-        <v>144</v>
+        <v>-343</v>
       </c>
       <c r="K7" t="n">
         <v>475</v>
@@ -1407,20 +1500,12 @@
         <v>25038</v>
       </c>
       <c r="M7" t="n">
-        <v>124329</v>
+        <v>102003</v>
       </c>
       <c r="N7" t="n">
         <v>-6483125</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1429,12 +1514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,47 +1528,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>128</v>
+        <v>1600</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>3.64</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>296360</v>
+        <v>8456</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>16744</v>
+        <v>547</v>
       </c>
       <c r="H8" t="n">
-        <v>-22626</v>
+        <v>-1421</v>
       </c>
       <c r="I8" t="n">
-        <v>604</v>
+        <v>147</v>
       </c>
       <c r="J8" t="n">
-        <v>34</v>
+        <v>-300</v>
       </c>
       <c r="K8" t="n">
-        <v>5516</v>
+        <v>232</v>
       </c>
       <c r="L8" t="n">
-        <v>135656</v>
+        <v>2454</v>
       </c>
       <c r="M8" t="n">
-        <v>637585</v>
+        <v>8173</v>
       </c>
       <c r="N8" t="n">
-        <v>-1116236</v>
-      </c>
-      <c r="O8" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140153</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1492,12 +1569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1506,47 +1583,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2700</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
+        <v>1565</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6.46</v>
       </c>
       <c r="F9" t="n">
-        <v>2925</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>-349</v>
+        <v>5154</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>141</v>
       </c>
       <c r="H9" t="n">
-        <v>-1006</v>
+        <v>-597</v>
       </c>
       <c r="I9" t="n">
-        <v>-77</v>
+        <v>366</v>
       </c>
       <c r="J9" t="n">
-        <v>903</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="L9" t="n">
-        <v>1905</v>
+        <v>3448</v>
       </c>
       <c r="M9" t="n">
-        <v>9503</v>
+        <v>12706</v>
       </c>
       <c r="N9" t="n">
-        <v>-89519</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106285</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1555,12 +1624,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1569,47 +1638,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3300</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>3.45</v>
+        <v>2700</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2078</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>407</v>
+        <v>2925</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-349</v>
       </c>
       <c r="H10" t="n">
-        <v>859</v>
+        <v>-509</v>
       </c>
       <c r="I10" t="n">
-        <v>-56</v>
+        <v>-77</v>
       </c>
       <c r="J10" t="n">
-        <v>-205</v>
+        <v>458</v>
       </c>
       <c r="K10" t="n">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>5685</v>
+        <v>1905</v>
       </c>
       <c r="M10" t="n">
-        <v>29353</v>
+        <v>7983</v>
       </c>
       <c r="N10" t="n">
-        <v>-19750</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89519</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1644,13 +1705,13 @@
         <v>195</v>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>-15</v>
       </c>
       <c r="I11" t="n">
         <v>-68</v>
       </c>
       <c r="J11" t="n">
-        <v>-291</v>
+        <v>-6</v>
       </c>
       <c r="K11" t="n">
         <v>24</v>
@@ -1659,20 +1720,12 @@
         <v>4157</v>
       </c>
       <c r="M11" t="n">
-        <v>21996</v>
+        <v>17340</v>
       </c>
       <c r="N11" t="n">
         <v>-19422</v>
       </c>
-      <c r="O11" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1681,58 +1734,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1440</v>
+        <v>7220</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6.67</v>
+        <v>9.06</v>
       </c>
       <c r="F12" t="n">
-        <v>787</v>
+        <v>433</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>-1019</v>
+        <v>-75</v>
       </c>
       <c r="I12" t="n">
-        <v>114</v>
+        <v>-10</v>
       </c>
       <c r="J12" t="n">
-        <v>1146</v>
+        <v>128</v>
       </c>
       <c r="K12" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>-197</v>
+        <v>250</v>
       </c>
       <c r="M12" t="n">
-        <v>-385</v>
+        <v>1004</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8982</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1741,12 +1789,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1755,44 +1803,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>139.5</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2.57</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>2117</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>455</v>
+        <v>88</v>
       </c>
       <c r="H13" t="n">
-        <v>889</v>
+        <v>70</v>
       </c>
       <c r="I13" t="n">
-        <v>-99</v>
+        <v>114</v>
       </c>
       <c r="J13" t="n">
-        <v>-501</v>
+        <v>-188</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>-197</v>
       </c>
       <c r="M13" t="n">
-        <v>-185</v>
+        <v>-725</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1815,25 +1858,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>383</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>-3.04</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>27553</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-1988</v>
       </c>
       <c r="H14" t="n">
-        <v>-3114</v>
+        <v>-3107</v>
       </c>
       <c r="I14" t="n">
         <v>-2343</v>
       </c>
       <c r="J14" t="n">
-        <v>-2556</v>
+        <v>-2342</v>
       </c>
       <c r="K14" t="n">
         <v>-45</v>
@@ -1842,17 +1885,12 @@
         <v>1207</v>
       </c>
       <c r="M14" t="n">
-        <v>-137</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1861,12 +1899,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1875,44 +1913,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1435</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-0.6899999999999999</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>455</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-72</v>
+        <v>-153</v>
       </c>
       <c r="H15" t="n">
-        <v>-126</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1</v>
+        <v>631</v>
       </c>
       <c r="J15" t="n">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-6</v>
+        <v>-28</v>
       </c>
       <c r="L15" t="n">
-        <v>-11</v>
+        <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>-155</v>
+        <v>-389</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1921,526 +1951,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>186</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>-3.12</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>4968</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>70</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-108</v>
       </c>
       <c r="H16" t="n">
-        <v>-531</v>
+        <v>62</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>161</v>
+      </c>
+      <c r="M16" t="n">
+        <v>190</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>4630</v>
-      </c>
-      <c r="M16" t="n">
-        <v>21608</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-11921</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8456</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>547</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-1403</v>
-      </c>
-      <c r="I17" t="n">
-        <v>147</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-112</v>
-      </c>
-      <c r="K17" t="n">
-        <v>232</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2454</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9655</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-140153</v>
-      </c>
-      <c r="O17" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>888</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1238</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-2772</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>424</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-107</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>938</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2822</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>-877</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-4039</v>
-      </c>
-      <c r="I19" t="n">
-        <v>17</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-490</v>
-      </c>
-      <c r="K19" t="n">
-        <v>179</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2706</v>
-      </c>
-      <c r="M19" t="n">
-        <v>10644</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-47629</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-8.56</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1110</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="F20" t="n">
-        <v>992</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H20" t="n">
-        <v>116</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>161</v>
-      </c>
-      <c r="M20" t="n">
-        <v>81</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>700</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1457</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>-153</v>
-      </c>
-      <c r="H21" t="n">
-        <v>325</v>
-      </c>
-      <c r="J21" t="n">
-        <v>144</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-28</v>
-      </c>
-      <c r="L21" t="n">
-        <v>51</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-266</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>260.5</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4779</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>288</v>
-      </c>
-      <c r="H22" t="n">
-        <v>469</v>
-      </c>
-      <c r="J22" t="n">
-        <v>52</v>
-      </c>
-      <c r="K22" t="n">
-        <v>117</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7047</v>
-      </c>
-      <c r="M22" t="n">
-        <v>36945</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-58879</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>7220</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>9.06</v>
-      </c>
-      <c r="E23" t="n">
-        <v>433</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="G23" t="n">
-        <v>37</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I23" t="n">
-        <v>65</v>
-      </c>
-      <c r="J23" t="n">
-        <v>20</v>
-      </c>
-      <c r="K23" t="n">
-        <v>250</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1254</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-8982</v>
-      </c>
-      <c r="N23" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1565</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5154</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>141</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-899</v>
-      </c>
-      <c r="H24" t="n">
-        <v>366</v>
-      </c>
-      <c r="I24" t="n">
-        <v>642</v>
-      </c>
-      <c r="J24" t="n">
-        <v>61</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3448</v>
-      </c>
-      <c r="L24" t="n">
-        <v>16154</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-106285</v>
-      </c>
-      <c r="N24" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260318.xlsx
+++ b/outputs/monitor_xlsx/20260318.xlsx
@@ -544,10 +544,6 @@
           <t>+1.51%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+2.61%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+1.37%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+1.38%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-2.22%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.17%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>-0.53%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+12.16%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+0.11%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>90.21億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-136.56億</t>
@@ -811,7 +774,6 @@
           <t>-2.88億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>7.09億</t>
@@ -822,8 +784,6 @@
           <t>35.45億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>149.34%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>186.96億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>14569口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>14461口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-68.05億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-51.45億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>349</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>744</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-3262</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1165</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8795</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42255</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21968</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260318.xlsx
+++ b/outputs/monitor_xlsx/20260318.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>77.8</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>78000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-5532</v>
       </c>
       <c r="H4" t="n">
-        <v>-92176</v>
+        <v>-207349</v>
       </c>
       <c r="I4" t="n">
         <v>2000</v>
       </c>
       <c r="J4" t="n">
-        <v>5150</v>
+        <v>9979</v>
       </c>
       <c r="K4" t="n">
         <v>13655</v>
@@ -1279,11 +1278,14 @@
         <v>12630</v>
       </c>
       <c r="M4" t="n">
-        <v>54076</v>
+        <v>66706</v>
       </c>
       <c r="N4" t="n">
         <v>-4479813</v>
       </c>
+      <c r="O4" t="n">
+        <v>0.76</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>929</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0.87</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>2473</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>-229</v>
+        <v>-712</v>
       </c>
       <c r="I5" t="n">
         <v>-2</v>
       </c>
       <c r="J5" t="n">
-        <v>-156</v>
+        <v>-250</v>
       </c>
       <c r="K5" t="n">
         <v>36</v>
@@ -1334,11 +1336,14 @@
         <v>2923</v>
       </c>
       <c r="M5" t="n">
-        <v>11281</v>
+        <v>14204</v>
       </c>
       <c r="N5" t="n">
         <v>-78826</v>
       </c>
+      <c r="O5" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1465</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1.74</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>11442</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1386</v>
       </c>
       <c r="H6" t="n">
-        <v>3734</v>
+        <v>4258</v>
       </c>
       <c r="I6" t="n">
         <v>53</v>
       </c>
       <c r="J6" t="n">
-        <v>-180</v>
+        <v>-627</v>
       </c>
       <c r="K6" t="n">
         <v>366</v>
@@ -1389,11 +1394,14 @@
         <v>5501</v>
       </c>
       <c r="M6" t="n">
-        <v>23315</v>
+        <v>28816</v>
       </c>
       <c r="N6" t="n">
         <v>-649114</v>
       </c>
+      <c r="O6" t="n">
+        <v>9.390000000000001</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1905</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1.87</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>25694</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>373</v>
       </c>
       <c r="H7" t="n">
-        <v>-32020</v>
+        <v>-47820</v>
       </c>
       <c r="I7" t="n">
         <v>-144</v>
       </c>
       <c r="J7" t="n">
-        <v>-343</v>
+        <v>-1289</v>
       </c>
       <c r="K7" t="n">
         <v>475</v>
@@ -1444,11 +1452,14 @@
         <v>25038</v>
       </c>
       <c r="M7" t="n">
-        <v>102003</v>
+        <v>127041</v>
       </c>
       <c r="N7" t="n">
         <v>-6483125</v>
       </c>
+      <c r="O7" t="n">
+        <v>0.21</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1600</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>8456</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>547</v>
       </c>
       <c r="H8" t="n">
-        <v>-1421</v>
+        <v>-1643</v>
       </c>
       <c r="I8" t="n">
         <v>147</v>
       </c>
       <c r="J8" t="n">
-        <v>-300</v>
+        <v>-406</v>
       </c>
       <c r="K8" t="n">
         <v>232</v>
@@ -1499,11 +1510,14 @@
         <v>2454</v>
       </c>
       <c r="M8" t="n">
-        <v>8173</v>
+        <v>10627</v>
       </c>
       <c r="N8" t="n">
         <v>-140153</v>
       </c>
+      <c r="O8" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1565</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>6.46</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>5154</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>141</v>
       </c>
       <c r="H9" t="n">
-        <v>-597</v>
+        <v>-899</v>
       </c>
       <c r="I9" t="n">
         <v>366</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>642</v>
       </c>
       <c r="K9" t="n">
         <v>61</v>
@@ -1554,11 +1568,14 @@
         <v>3448</v>
       </c>
       <c r="M9" t="n">
-        <v>12706</v>
+        <v>16154</v>
       </c>
       <c r="N9" t="n">
         <v>-106285</v>
       </c>
+      <c r="O9" t="n">
+        <v>16.92</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1587,20 +1604,20 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>2925</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>-349</v>
       </c>
       <c r="H10" t="n">
-        <v>-509</v>
+        <v>-1683</v>
       </c>
       <c r="I10" t="n">
         <v>-77</v>
       </c>
       <c r="J10" t="n">
-        <v>458</v>
+        <v>362</v>
       </c>
       <c r="K10" t="n">
         <v>28</v>
@@ -1609,11 +1626,14 @@
         <v>1905</v>
       </c>
       <c r="M10" t="n">
-        <v>7983</v>
+        <v>9888</v>
       </c>
       <c r="N10" t="n">
         <v>-89519</v>
       </c>
+      <c r="O10" t="n">
+        <v>13.37</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1850</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>593</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>195</v>
       </c>
       <c r="H11" t="n">
-        <v>-15</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
         <v>-68</v>
       </c>
       <c r="J11" t="n">
-        <v>-6</v>
+        <v>-82</v>
       </c>
       <c r="K11" t="n">
         <v>24</v>
@@ -1664,11 +1684,14 @@
         <v>4157</v>
       </c>
       <c r="M11" t="n">
-        <v>17340</v>
+        <v>21497</v>
       </c>
       <c r="N11" t="n">
         <v>-19422</v>
       </c>
+      <c r="O11" t="n">
+        <v>-4.18</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7220</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>9.06</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>433</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>-75</v>
+        <v>37</v>
       </c>
       <c r="I12" t="n">
         <v>-10</v>
       </c>
       <c r="J12" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
@@ -1719,11 +1742,14 @@
         <v>250</v>
       </c>
       <c r="M12" t="n">
-        <v>1004</v>
+        <v>1254</v>
       </c>
       <c r="N12" t="n">
         <v>-8982</v>
       </c>
+      <c r="O12" t="n">
+        <v>34.68</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>88</v>
       </c>
       <c r="H13" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="I13" t="n">
         <v>114</v>
       </c>
       <c r="J13" t="n">
-        <v>-188</v>
+        <v>-85</v>
       </c>
       <c r="K13" t="n">
         <v>90</v>
@@ -1774,11 +1800,14 @@
         <v>-197</v>
       </c>
       <c r="M13" t="n">
-        <v>-725</v>
+        <v>-922</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-1988</v>
       </c>
       <c r="H14" t="n">
-        <v>-3107</v>
+        <v>-5100</v>
       </c>
       <c r="I14" t="n">
         <v>-2343</v>
       </c>
       <c r="J14" t="n">
-        <v>-2342</v>
+        <v>-5332</v>
       </c>
       <c r="K14" t="n">
         <v>-45</v>
@@ -1829,11 +1858,14 @@
         <v>1207</v>
       </c>
       <c r="M14" t="n">
-        <v>21</v>
+        <v>1228</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1856,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-153</v>
       </c>
       <c r="H15" t="n">
-        <v>631</v>
+        <v>856</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1881,11 +1916,14 @@
         <v>51</v>
       </c>
       <c r="M15" t="n">
-        <v>-389</v>
+        <v>-338</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-108</v>
       </c>
       <c r="H16" t="n">
-        <v>62</v>
+        <v>84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1933,11 +1974,14 @@
         <v>161</v>
       </c>
       <c r="M16" t="n">
-        <v>190</v>
+        <v>351</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>349</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>5.44</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>744</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-48</v>
       </c>
-      <c r="G17" t="n">
-        <v>-3262</v>
-      </c>
       <c r="H17" t="n">
+        <v>-1417</v>
+      </c>
+      <c r="I17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="n">
-        <v>1165</v>
-      </c>
       <c r="J17" t="n">
+        <v>675</v>
+      </c>
+      <c r="K17" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8795</v>
       </c>
-      <c r="L17" t="n">
-        <v>42255</v>
-      </c>
       <c r="M17" t="n">
+        <v>43603</v>
+      </c>
+      <c r="N17" t="n">
         <v>-21968</v>
       </c>
-      <c r="N17" t="n">
-        <v>14.76</v>
+      <c r="O17" t="n">
+        <v>14.8</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260318.xlsx
+++ b/outputs/monitor_xlsx/20260318.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>14.8</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6292</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-921</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-6359</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-156</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1008</v>
+      </c>
+      <c r="K18" t="n">
+        <v>174</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5954</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29824</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400951</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>580</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50602</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>6762</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18031</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1352</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1487</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35419</v>
+      </c>
+      <c r="M19" t="n">
+        <v>179644</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-391733</v>
+      </c>
+      <c r="O19" t="n">
+        <v>21.97</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>567</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18629</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-486</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-10354</v>
+      </c>
+      <c r="I20" t="n">
+        <v>339</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6080</v>
+      </c>
+      <c r="K20" t="n">
+        <v>778</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10803</v>
+      </c>
+      <c r="M20" t="n">
+        <v>48699</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161234</v>
+      </c>
+      <c r="O20" t="n">
+        <v>15.11</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
